--- a/APS-Modules/aps-mp/src/main/resources/excelModel/demandPlanSumExportTemplate.xlsx
+++ b/APS-Modules/aps-mp/src/main/resources/excelModel/demandPlanSumExportTemplate.xlsx
@@ -35,7 +35,7 @@
     <t>{title}</t>
   </si>
   <si>
-    <t>版本号：{structureName}</t>
+    <t>版本号：{monthPlanVersion}</t>
   </si>
   <si>
     <t>合计</t>
@@ -164,7 +164,7 @@
     <t>{isProduction}</t>
   </si>
   <si>
-    <t>{updateDate}</t>
+    <t>{updateTime}</t>
   </si>
   <si>
     <t>{.factoryName}</t>
@@ -16505,7 +16505,7 @@
     <extLst/>
   </autoFilter>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C5:C102 D5:D102 I5:I102 J5:J102 Y5:Y102 AA5:AA102">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Y5:Y102 AA5:AA102 C5:D102 I5:J102">
       <formula1>#REF!</formula1>
     </dataValidation>
   </dataValidations>
